--- a/data/trans_orig/IP07KS_C09_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C09_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ir bien en el colegio en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de ir bien en el colegio, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25239</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17496</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35630</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13596</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9214</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26124</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>40300</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>54302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7047</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21668</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14276</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9729</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18846</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11147</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6365</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2938</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5740</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52465</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42194</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63316</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32481</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26230</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37698</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39143</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83443</t>
+          <t>87802</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70201</t>
+          <t>74995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94441</t>
+          <t>100455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34325</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44507</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15030</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9787</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20403</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61196</t>
+          <t>60959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1628,74 +1628,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10975</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25003</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9520</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10155</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>17,75%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30916</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>30,08%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -1741,97 +1741,97 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11470</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34439</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24417</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42783</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21208</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36949</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,38%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>22540</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45103</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>56980</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75815</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21948</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14448</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20819</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7646</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37049</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>53188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21325</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32,89%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>29318</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2590</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>82736</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2639</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27545</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>34273</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>49,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>62,14%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>23729</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>17517</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>30530</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34611</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60047</t>
+          <t>62719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20250</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14299</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26301</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>47,69%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>25616</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>19517</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>31550</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>58,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56168</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2639</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10898</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6945</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55155</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55155</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55155</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55621</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55621</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55621</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>139688</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>122386</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>159358</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>91014</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>60109</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>109311</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>97705</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>85497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161101</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>231345</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>188453</t>
+          <t>214525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>257901</t>
+          <t>261113</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>90894</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>75412</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>104945</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>75741</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>47941</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>93094</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>44,23%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>91663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>166154</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>148413</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188261</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>31227</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>20595</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>48641</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>12588</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>101484</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>72730</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>7707</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,27 +3975,27 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
